--- a/countries/li/2015-2019.xlsx
+++ b/countries/li/2015-2019.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>5.347593582887701</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_LI_ECDC_TUBE_ANNUAL</t>
@@ -790,12 +785,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -806,11 +796,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -875,7 +860,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -910,12 +895,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2015-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -924,99 +909,19 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
+      <c r="R3" t="n">
+        <v>5.317027781470158</v>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_LI_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_LI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:LI:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1024,12 +929,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1040,11 +940,6 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1124,22 +1019,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1161,14 +1056,9 @@
       <c r="R4" t="n">
         <v>5.317027781470158</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1183,27 +1073,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1268,7 +1148,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1303,113 +1183,33 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.64197302545541</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_LI_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_LI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:LI:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1417,12 +1217,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1433,11 +1228,6 @@
       <c r="AT5" t="n">
         <v>1</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1537,12 +1327,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1552,12 +1342,7 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>5.317027781470158</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5.283946050910821</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1576,12 +1361,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1592,11 +1372,6 @@
       <c r="AT6" t="n">
         <v>1</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1661,7 +1436,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1676,68 +1451,46 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.622710046290832</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_LI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>HIV infection</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1745,64 +1498,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:LI:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1810,27 +1505,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1867,1185 +1552,6 @@
         </is>
       </c>
       <c r="BC7" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>D025</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>肺结核</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.64197302545541</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>D025</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>肺结核</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_LI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:LI:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>D162</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>HIV infection</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>人类免疫缺乏病毒感染</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5.283946050910821</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>D162</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>HIV infection</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>人类免疫缺乏病毒感染</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_LI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>HIV infection</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:LI:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>D025</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>肺结核</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2018-01</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.622710046290832</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>li</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Liechtenstein</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>D025</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>肺结核</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2018-01</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_LI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:LI:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -3177,7 +1683,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -3197,7 +1703,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3207,7 +1713,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/countries/li/2015-2019.xlsx
+++ b/countries/li/2015-2019.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>5.347593582887701</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_LI_ECDC_TUBE_ANNUAL</t>
@@ -785,7 +790,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -795,6 +805,11 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -860,7 +875,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -895,12 +910,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -909,19 +924,99 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>5.317027781470158</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_LI_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -929,7 +1024,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -939,6 +1039,11 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1019,22 +1124,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1056,9 +1161,14 @@
       <c r="R4" t="n">
         <v>5.317027781470158</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1073,16 +1183,26 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1148,7 +1268,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1183,33 +1303,113 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.64197302545541</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1217,7 +1417,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1227,6 +1432,11 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1327,12 +1537,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1342,7 +1552,12 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>5.283946050910821</v>
+        <v>5.317027781470158</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1361,7 +1576,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1371,6 +1591,11 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1436,7 +1661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1451,53 +1676,133 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.622710046290832</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1505,17 +1810,27 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1552,6 +1867,1185 @@
         </is>
       </c>
       <c r="BC7" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.64197302545541</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.283946050910821</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.622710046290832</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -1683,7 +3177,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1703,7 +3197,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1713,7 +3207,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
